--- a/artfynd/A 29061-2023 artfynd.xlsx
+++ b/artfynd/A 29061-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29061-2023 artfynd.xlsx
+++ b/artfynd/A 29061-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>66490929</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547996.6624943148</v>
+        <v>547997</v>
       </c>
       <c r="R2" t="n">
-        <v>7111935.343212973</v>
+        <v>7111935</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66490922</v>
+        <v>66490939</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548050.4401023292</v>
+        <v>547722</v>
       </c>
       <c r="R3" t="n">
-        <v>7111965.007613786</v>
+        <v>7112278</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +849,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,50 +883,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66490923</v>
+        <v>66490925</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aspberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547952.8385024056</v>
+        <v>547935</v>
       </c>
       <c r="R4" t="n">
-        <v>7111940.780652527</v>
+        <v>7111931</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,21 +955,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,50 +989,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66490931</v>
+        <v>66490930</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aspberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547996.6624943148</v>
+        <v>547997</v>
       </c>
       <c r="R5" t="n">
-        <v>7111935.343212973</v>
+        <v>7111935</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,21 +1061,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1147,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66490930</v>
+        <v>66490922</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,38 +1106,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Aspberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547996.6624943148</v>
+        <v>548050</v>
       </c>
       <c r="R6" t="n">
-        <v>7111935.343212973</v>
+        <v>7111965</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1224,21 +1163,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1250,7 +1179,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1268,15 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66490925</v>
+        <v>66490924</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,26 +1208,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1312,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547934.6140203631</v>
+        <v>547935</v>
       </c>
       <c r="R7" t="n">
-        <v>7111931.325166186</v>
+        <v>7111931</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1345,21 +1269,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1371,7 +1285,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,15 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66490939</v>
+        <v>66490931</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547722.3940445574</v>
+        <v>547997</v>
       </c>
       <c r="R8" t="n">
-        <v>7112277.501321459</v>
+        <v>7111935</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1462,21 +1371,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1488,7 +1387,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1506,15 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66490924</v>
+        <v>66490938</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,21 +1433,17 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Aspberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>547934.6140203631</v>
+        <v>547722</v>
       </c>
       <c r="R9" t="n">
-        <v>7111931.325166186</v>
+        <v>7112278</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1583,21 +1473,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1609,7 +1489,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,15 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66490938</v>
+        <v>66490923</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>547722.3940445574</v>
+        <v>547953</v>
       </c>
       <c r="R10" t="n">
-        <v>7112277.501321459</v>
+        <v>7111941</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1700,21 +1575,11 @@
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2010-06-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1726,7 +1591,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 29061-2023 artfynd.xlsx
+++ b/artfynd/A 29061-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490929</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490925</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490930</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490931</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490938</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,8 +1651,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66490923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>